--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.01185640790814534</v>
       </c>
       <c r="C2" t="n">
-        <v>12425544</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12425544</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>9629464</v>
+        <v>4708088</v>
       </c>
       <c r="L2" t="n">
-        <v>6135748</v>
+        <v>2928103</v>
       </c>
       <c r="M2" t="n">
-        <v>1715503</v>
+        <v>794464</v>
       </c>
       <c r="N2" t="n">
-        <v>122816</v>
+        <v>50490</v>
       </c>
       <c r="O2" t="n">
-        <v>966785</v>
+        <v>458582</v>
       </c>
       <c r="P2" t="n">
-        <v>373025</v>
+        <v>179951</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999940395355225</v>
+        <v>0.9999903440475464</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9780199527740479</v>
+        <v>0.9563698172569275</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9509601593017578</v>
+        <v>0.9075567722320557</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9181236624717712</v>
+        <v>0.8505728840827942</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8481650948524475</v>
+        <v>0.6981760859489441</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9504075646400452</v>
+        <v>0.9017051458358765</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9648312926292419</v>
+        <v>0.930397629737854</v>
       </c>
       <c r="X2" t="n">
-        <v>12425544</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12425544</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>9257922</v>
+        <v>4535637</v>
       </c>
       <c r="AG2" t="n">
-        <v>5602510</v>
+        <v>2682458</v>
       </c>
       <c r="AH2" t="n">
-        <v>1500791</v>
+        <v>705093</v>
       </c>
       <c r="AI2" t="n">
-        <v>103745</v>
+        <v>45132</v>
       </c>
       <c r="AJ2" t="n">
-        <v>876959</v>
+        <v>418529</v>
       </c>
       <c r="AK2" t="n">
-        <v>348888</v>
+        <v>168879</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9374659061431885</v>
+        <v>0.9185657501220703</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.8742755651473999</v>
+        <v>0.8371988534927368</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8102678060531616</v>
+        <v>0.7613507509231567</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.5869390368461609</v>
+        <v>0.5106700658798218</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.8630568981170654</v>
+        <v>0.8237884044647217</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9026249051094055</v>
+        <v>0.8738299608230591</v>
       </c>
     </row>
     <row r="3">
@@ -795,13 +795,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>9629464</v>
+        <v>4708088</v>
       </c>
       <c r="E3" t="n">
-        <v>213210</v>
+        <v>203627</v>
       </c>
       <c r="F3" t="n">
-        <v>10475</v>
+        <v>10472</v>
       </c>
       <c r="G3" t="n">
         <v>2493</v>
@@ -813,109 +813,109 @@
         <v>44</v>
       </c>
       <c r="J3" t="n">
-        <v>19715182</v>
+        <v>9857568</v>
       </c>
       <c r="K3" t="n">
-        <v>22068645</v>
+        <v>10930834</v>
       </c>
       <c r="L3" t="n">
-        <v>25400866</v>
+        <v>12557989</v>
       </c>
       <c r="M3" t="n">
-        <v>30132447</v>
+        <v>15002642</v>
       </c>
       <c r="N3" t="n">
-        <v>31941794</v>
+        <v>15960021</v>
       </c>
       <c r="O3" t="n">
-        <v>31073293</v>
+        <v>15511740</v>
       </c>
       <c r="P3" t="n">
-        <v>31740658</v>
+        <v>15863656</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9770410060882568</v>
+        <v>0.9559996724128723</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9552001357078552</v>
+        <v>0.9110021591186523</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9246160387992859</v>
+        <v>0.8559300303459167</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6937972903251648</v>
+        <v>0.570173442363739</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9505683183670044</v>
+        <v>0.901531457901001</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9650234580039978</v>
+        <v>0.9310282468795776</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9257922</v>
+        <v>4535637</v>
       </c>
       <c r="Z3" t="n">
-        <v>557637</v>
+        <v>363917</v>
       </c>
       <c r="AA3" t="n">
-        <v>23072</v>
+        <v>14825</v>
       </c>
       <c r="AB3" t="n">
-        <v>16910</v>
+        <v>10241</v>
       </c>
       <c r="AC3" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AD3" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="AE3" t="n">
-        <v>19715256</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>21667504</v>
+        <v>10743519</v>
       </c>
       <c r="AG3" t="n">
-        <v>24911615</v>
+        <v>12334615</v>
       </c>
       <c r="AH3" t="n">
-        <v>29934007</v>
+        <v>14921197</v>
       </c>
       <c r="AI3" t="n">
-        <v>31890769</v>
+        <v>15938602</v>
       </c>
       <c r="AJ3" t="n">
-        <v>30984591</v>
+        <v>15472205</v>
       </c>
       <c r="AK3" t="n">
-        <v>31716617</v>
+        <v>15852734</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9393429756164551</v>
+        <v>0.9209826588630676</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.8721867799758911</v>
+        <v>0.8345761895179749</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8088912963867188</v>
+        <v>0.759644627571106</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.5860637426376343</v>
+        <v>0.5096666216850281</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.8622490167617798</v>
+        <v>0.822790801525116</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9025805592536926</v>
+        <v>0.8737440705299377</v>
       </c>
     </row>
     <row r="4">
@@ -929,16 +929,16 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>202113</v>
+        <v>200531</v>
       </c>
       <c r="E4" t="n">
-        <v>6135748</v>
+        <v>2928103</v>
       </c>
       <c r="F4" t="n">
-        <v>82054</v>
+        <v>81920</v>
       </c>
       <c r="G4" t="n">
-        <v>2371</v>
+        <v>2367</v>
       </c>
       <c r="H4" t="n">
         <v>1141</v>
@@ -947,109 +947,109 @@
         <v>92</v>
       </c>
       <c r="J4" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="K4" t="n">
-        <v>216413</v>
+        <v>214786</v>
       </c>
       <c r="L4" t="n">
-        <v>316413</v>
+        <v>298255</v>
       </c>
       <c r="M4" t="n">
-        <v>152985</v>
+        <v>139570</v>
       </c>
       <c r="N4" t="n">
-        <v>21986</v>
+        <v>21827</v>
       </c>
       <c r="O4" t="n">
-        <v>50447</v>
+        <v>49990</v>
       </c>
       <c r="P4" t="n">
-        <v>13597</v>
+        <v>13462</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999970197677612</v>
+        <v>0.9999951720237732</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9775301814079285</v>
+        <v>0.9561846852302551</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9530754089355469</v>
+        <v>0.9092761874198914</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9213584065437317</v>
+        <v>0.8532430529594421</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7632542252540588</v>
+        <v>0.6277157068252563</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9504879117012024</v>
+        <v>0.9016183018684387</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9649273753166199</v>
+        <v>0.930712878704071</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>581677</v>
+        <v>380423</v>
       </c>
       <c r="Z4" t="n">
-        <v>5602510</v>
+        <v>2682458</v>
       </c>
       <c r="AA4" t="n">
-        <v>217409</v>
+        <v>135949</v>
       </c>
       <c r="AB4" t="n">
-        <v>14377</v>
+        <v>8964</v>
       </c>
       <c r="AC4" t="n">
-        <v>7078</v>
+        <v>5960</v>
       </c>
       <c r="AD4" t="n">
-        <v>470</v>
+        <v>402</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>617554</v>
+        <v>402101</v>
       </c>
       <c r="AG4" t="n">
-        <v>805664</v>
+        <v>521629</v>
       </c>
       <c r="AH4" t="n">
-        <v>351425</v>
+        <v>221015</v>
       </c>
       <c r="AI4" t="n">
-        <v>73011</v>
+        <v>43246</v>
       </c>
       <c r="AJ4" t="n">
-        <v>139149</v>
+        <v>89525</v>
       </c>
       <c r="AK4" t="n">
-        <v>37638</v>
+        <v>24384</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9384034872055054</v>
+        <v>0.9197726845741272</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.8732299208641052</v>
+        <v>0.8358854055404663</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8095789551734924</v>
+        <v>0.7604967355728149</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.5865010619163513</v>
+        <v>0.5101678967475891</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.8626527786254883</v>
+        <v>0.8232892751693726</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9026026725769043</v>
+        <v>0.873786985874176</v>
       </c>
     </row>
     <row r="5">
@@ -1059,19 +1059,19 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>7963</v>
+        <v>7934</v>
       </c>
       <c r="E5" t="n">
-        <v>92910</v>
+        <v>86877</v>
       </c>
       <c r="F5" t="n">
-        <v>1715503</v>
+        <v>794464</v>
       </c>
       <c r="G5" t="n">
-        <v>9234</v>
+        <v>9157</v>
       </c>
       <c r="H5" t="n">
-        <v>29089</v>
+        <v>29087</v>
       </c>
       <c r="I5" t="n">
         <v>667</v>
@@ -1080,106 +1080,106 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>226278</v>
+        <v>216692</v>
       </c>
       <c r="L5" t="n">
-        <v>287773</v>
+        <v>286053</v>
       </c>
       <c r="M5" t="n">
-        <v>139865</v>
+        <v>133724</v>
       </c>
       <c r="N5" t="n">
-        <v>54204</v>
+        <v>38062</v>
       </c>
       <c r="O5" t="n">
-        <v>50275</v>
+        <v>50088</v>
       </c>
       <c r="P5" t="n">
-        <v>13520</v>
+        <v>13331</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999976754188538</v>
+        <v>0.9999962449073792</v>
       </c>
       <c r="R5" t="n">
-        <v>0.986226499080658</v>
+        <v>0.9731507897377014</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9812018871307373</v>
+        <v>0.9636407494544983</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9908885359764099</v>
+        <v>0.9829939603805542</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9976294636726379</v>
+        <v>0.9962733387947083</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9968662261962891</v>
+        <v>0.9937725067138672</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9991562962532043</v>
+        <v>0.9983327984809875</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>20020</v>
+        <v>12213</v>
       </c>
       <c r="Z5" t="n">
-        <v>227430</v>
+        <v>143254</v>
       </c>
       <c r="AA5" t="n">
-        <v>1500791</v>
+        <v>705093</v>
       </c>
       <c r="AB5" t="n">
-        <v>23338</v>
+        <v>13468</v>
       </c>
       <c r="AC5" t="n">
-        <v>80709</v>
+        <v>51713</v>
       </c>
       <c r="AD5" t="n">
-        <v>3080</v>
+        <v>2447</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>597820</v>
+        <v>389143</v>
       </c>
       <c r="AG5" t="n">
-        <v>821011</v>
+        <v>531698</v>
       </c>
       <c r="AH5" t="n">
-        <v>354577</v>
+        <v>223095</v>
       </c>
       <c r="AI5" t="n">
-        <v>73275</v>
+        <v>43420</v>
       </c>
       <c r="AJ5" t="n">
-        <v>140101</v>
+        <v>90141</v>
       </c>
       <c r="AK5" t="n">
-        <v>37657</v>
+        <v>24403</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9621859192848206</v>
+        <v>0.9507638812065125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9493891000747681</v>
+        <v>0.9344554543495178</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9780340790748596</v>
+        <v>0.9723647236824036</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9954485893249512</v>
+        <v>0.9946070909500122</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9913116693496704</v>
+        <v>0.9888200759887695</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9976573586463928</v>
+        <v>0.996964156627655</v>
       </c>
     </row>
     <row r="6">
@@ -1189,22 +1189,22 @@
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>6310</v>
+        <v>6294</v>
       </c>
       <c r="E6" t="n">
-        <v>9377</v>
+        <v>6835</v>
       </c>
       <c r="F6" t="n">
-        <v>30517</v>
+        <v>17239</v>
       </c>
       <c r="G6" t="n">
-        <v>122816</v>
+        <v>50490</v>
       </c>
       <c r="H6" t="n">
-        <v>7372</v>
+        <v>7085</v>
       </c>
       <c r="I6" t="n">
-        <v>604</v>
+        <v>585</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>15763</v>
+        <v>9406</v>
       </c>
       <c r="Z6" t="n">
-        <v>14260</v>
+        <v>9011</v>
       </c>
       <c r="AA6" t="n">
-        <v>25613</v>
+        <v>14794</v>
       </c>
       <c r="AB6" t="n">
-        <v>103745</v>
+        <v>45132</v>
       </c>
       <c r="AC6" t="n">
-        <v>16279</v>
+        <v>9330</v>
       </c>
       <c r="AD6" t="n">
-        <v>1360</v>
+        <v>879</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1272,13 +1272,13 @@
         <v>29610</v>
       </c>
       <c r="G7" t="n">
-        <v>7629</v>
+        <v>7558</v>
       </c>
       <c r="H7" t="n">
-        <v>966785</v>
+        <v>458582</v>
       </c>
       <c r="I7" t="n">
-        <v>12190</v>
+        <v>12074</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>6022</v>
+        <v>5213</v>
       </c>
       <c r="AA7" t="n">
-        <v>83790</v>
+        <v>54236</v>
       </c>
       <c r="AB7" t="n">
-        <v>17623</v>
+        <v>10075</v>
       </c>
       <c r="AC7" t="n">
-        <v>876959</v>
+        <v>418529</v>
       </c>
       <c r="AD7" t="n">
-        <v>32644</v>
+        <v>20602</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>22</v>
@@ -1346,13 +1346,13 @@
         <v>329</v>
       </c>
       <c r="G8" t="n">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="H8" t="n">
-        <v>12793</v>
+        <v>12625</v>
       </c>
       <c r="I8" t="n">
-        <v>373025</v>
+        <v>179951</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="Z8" t="n">
-        <v>315</v>
+        <v>234</v>
       </c>
       <c r="AA8" t="n">
-        <v>1541</v>
+        <v>1211</v>
       </c>
       <c r="AB8" t="n">
-        <v>763</v>
+        <v>498</v>
       </c>
       <c r="AC8" t="n">
-        <v>34966</v>
+        <v>22416</v>
       </c>
       <c r="AD8" t="n">
-        <v>348888</v>
+        <v>168879</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
